--- a/sync_project/orders_02_2025.xlsx
+++ b/sync_project/orders_02_2025.xlsx
@@ -523,253 +523,253 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Бюджетування: формування, коригування і консолідація плану</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Внесення в консолідований звіт по Групі бюджети компаній на 2025 р, https://docs.google.com/spreadsheets/d/1u0FVZO4JYWg7oxSWbrLPKiplvXBc5bwMFG9ryYCpb5o/edit?gid=907018591#gid=907018591&amp;range=A4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Netpeak Group</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>13-02-2025</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>28-02-2025</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Vadym Stamford Didenko</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>584</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Бюджетування: формування, коригування і консолідація плану</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Категорія В:
+коригування до бюджету</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>42.09</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1u0FVZO4JYWg7oxSWbrLPKiplvXBc5bwMFG9ryYCpb5o/edit?gid=907018591#gid=907018591&amp;range=A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Сформовано звіт надходжень та витрат від партнерів по контрагентам/регіонам/місяцям за попередній місяць, https://docs.google.com/spreadsheets/d/1F7S6VgN5qKEnnu8Glomad2l7MaRse36cU60QefjAXqE/edit?gid=1277721875#gid=1277721875</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>05-02-2025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>05-02-2025</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>580</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1F7S6VgN5qKEnnu8Glomad2l7MaRse36cU60QefjAXqE/edit?gid=1277721875#gid=1277721875</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Огляд звіту за січень по аналітикам (статтям/проєктам), http://img.netpeak.ua/sense/ZDNGHA.jpg</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): General</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>10-02-2025</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>10-02-2025</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L4" t="n">
         <v>581</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Категорія А:
 з фін. аналітиком</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>31.66</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>http://img.netpeak.ua/sense/ZDNGHA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Сформовано звіт надходжень та витрат від партнерів по контрагентам/регіонам/місяцям за попередній місяць, https://docs.google.com/spreadsheets/d/1F7S6VgN5qKEnnu8Glomad2l7MaRse36cU60QefjAXqE/edit?gid=1277721875#gid=1277721875</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>05-02-2025</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>05-02-2025</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>580</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1F7S6VgN5qKEnnu8Glomad2l7MaRse36cU60QefjAXqE/edit?gid=1277721875#gid=1277721875</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Бюджетування: формування, коригування і консолідація плану</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Внесення в консолідований звіт по Групі бюджети компаній на 2025 р, https://docs.google.com/spreadsheets/d/1u0FVZO4JYWg7oxSWbrLPKiplvXBc5bwMFG9ryYCpb5o/edit?gid=907018591#gid=907018591&amp;range=A4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Netpeak Group</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>13-02-2025</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>28-02-2025</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Vadym Stamford Didenko</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>584</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Бюджетування: формування, коригування і консолідація плану</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Категорія В:
-коригування до бюджету</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>42.09</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1u0FVZO4JYWg7oxSWbrLPKiplvXBc5bwMFG9ryYCpb5o/edit?gid=907018591#gid=907018591&amp;range=A4</t>
         </is>
       </c>
     </row>
@@ -781,169 +781,169 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Зроблено деталізацію виплаченої зарплати у січні, https://docs.google.com/spreadsheets/d/13Vn63vfrVdWmulHdWFCubcrjj0snvjNJuNyDjExBxo0/edit?gid=693268948#gid=693268948</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Asolytics</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10-02-2025</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Сергей Vert Брагаренко</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>545</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Категорія А:
+формування вибірки даних</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/13Vn63vfrVdWmulHdWFCubcrjj0snvjNJuNyDjExBxo0/edit?gid=693268948#gid=693268948</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1KK1-wrtGQPWTcdOzTaXDtY35D-a0pBLslq1QNRTv5bc/edit?gid=1890887847#gid=1890887847</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Netpeak Agency (KZ): SMM</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>572</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>23.66</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1KK1-wrtGQPWTcdOzTaXDtY35D-a0pBLslq1QNRTv5bc/edit?gid=1890887847#gid=1890887847</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Зроблено деталізацію виплаченої зарплати у січні, https://docs.google.com/spreadsheets/d/13Vn63vfrVdWmulHdWFCubcrjj0snvjNJuNyDjExBxo0/edit?gid=693268948#gid=693268948</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Asolytics</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10-02-2025</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Сергей Vert Брагаренко</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>545</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Категорія А:
-формування вибірки даних</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>5.80</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/13Vn63vfrVdWmulHdWFCubcrjj0snvjNJuNyDjExBxo0/edit?gid=693268948#gid=693268948</t>
         </is>
       </c>
     </row>
@@ -959,165 +959,165 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>Вигружені витрати  з IT-e, https://docs.google.com/spreadsheets/d/1mDvdh5zbtWpCmXyJqDmiwkWrjMHwcQbTG9Pw75lDrU4/edit?gid=1130421931#gid=1130421931</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>06-02-2025</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>06-02-2025</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>556</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1mDvdh5zbtWpCmXyJqDmiwkWrjMHwcQbTG9Pw75lDrU4/edit?gid=1130421931#gid=1130421931</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1_YlRQ8WA-yOr7353SXavEVUIQci2hpWUQDg0WAHDo8Q/edit?gid=2113057188#gid=2113057188</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): PPC</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>557</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>23.66</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1_YlRQ8WA-yOr7353SXavEVUIQci2hpWUQDg0WAHDo8Q/edit?gid=2113057188#gid=2113057188</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Вигружені витрати  з IT-e, https://docs.google.com/spreadsheets/d/1mDvdh5zbtWpCmXyJqDmiwkWrjMHwcQbTG9Pw75lDrU4/edit?gid=1130421931#gid=1130421931</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>06-02-2025</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>06-02-2025</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>556</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1mDvdh5zbtWpCmXyJqDmiwkWrjMHwcQbTG9Pw75lDrU4/edit?gid=1130421931#gid=1130421931</t>
         </is>
       </c>
     </row>
@@ -1215,341 +1215,341 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Не заповнено, https://docs.google.com/spreadsheets/d/1nr__kXUSm1gau-kxYRqKvRvsmn77jxxjQ22ATszKzfo/edit?gid=449082110#gid=449082110</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Serpstat</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17-02-2025</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Сергей Vert Брагаренко</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>546</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Категорія В:
-формування вибірки даних+аналіз</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>59.15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1nr__kXUSm1gau-kxYRqKvRvsmn77jxxjQ22ATszKzfo/edit?gid=449082110#gid=449082110</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Вигружені витрати  з IT-e, https://docs.google.com/spreadsheets/d/1r41uj0dHj2iLXBJoadcvnUlnH_ZLioNEwOQxil3kJcM/edit?gid=650784775#gid=650784775</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OLX: General</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>04-02-2025</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>05-02-2025</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1r41uj0dHj2iLXBJoadcvnUlnH_ZLioNEwOQxil3kJcM/edit?gid=650784775#gid=650784775</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Сформовано план надходжень в розрізі ФОПів на поточний місяць, перевірено що ліміти не будуть перевищені, повідомлено про це Гаріку і Косу. Якщо ліміти по якомусь фопу підходять, то підібрана заміна, узгоджена з Косом і Гаріком. Якщо немає відкритого валютного рахунку, то був зроблений запит на Стоїка про відкриття рахунку в банку. Поставлені задачі на відкриття фоп, якщо немає вільних для отримання виплат., https://docs.google.com/spreadsheets/d/1BrJuQMiOSnd79VRIUUmsDqT9gADTZk0ayQ5GwrY6EcM/edit#gid=602441903</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Tonti Laguna Prime</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10-02-2025</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Сергей Vert Брагаренко</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>541</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Категорія А:
-формування вибірки даних</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1BrJuQMiOSnd79VRIUUmsDqT9gADTZk0ayQ5GwrY6EcM/edit#gid=602441903</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1nAJRBHRaMTJB9N5L8tZSU3-pp1F9z_0WhVGylrB-loU/edit?gid=1868453835#gid=1868453835</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): SERM</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L10" t="n">
         <v>570</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1nAJRBHRaMTJB9N5L8tZSU3-pp1F9z_0WhVGylrB-loU/edit?gid=1868453835#gid=1868453835</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Бюджетування: формування, коригування і консолідація плану</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Перевірено бюджет та внесено у докс по CF, https://docs.google.com/spreadsheets/d/13sILq-kZJl1dWXiFRhmYHtKg94nYH2Z70eBIJ7Lc2hc/edit?gid=1684866700#gid=1684866700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tonti Laguna Prime</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Сергей Vert Брагаренко</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>547</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Бюджетування: формування, коригування і консолідація плану</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Категорія В:
+коригування до бюджету</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>28.06</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/13sILq-kZJl1dWXiFRhmYHtKg94nYH2Z70eBIJ7Lc2hc/edit?gid=1684866700#gid=1684866700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Вигружені витрати  з IT-e, https://docs.google.com/spreadsheets/d/1r41uj0dHj2iLXBJoadcvnUlnH_ZLioNEwOQxil3kJcM/edit?gid=650784775#gid=650784775</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OLX: General</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>04-02-2025</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>05-02-2025</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1r41uj0dHj2iLXBJoadcvnUlnH_ZLioNEwOQxil3kJcM/edit?gid=650784775#gid=650784775</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Бюджетування: формування, коригування і консолідація плану</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Перевірено бюджет та внесено у докс по CF, https://docs.google.com/spreadsheets/d/1o6ny97bUSd0JecsdBcnNSbmHQTZQETxla1QH6Ce87xk/edit?gid=16319423#gid=16319423</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Choice31</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Сергей Vert Брагаренко</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>550</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Бюджетування: формування, коригування і консолідація плану</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Категорія В:
+коригування до бюджету</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1nAJRBHRaMTJB9N5L8tZSU3-pp1F9z_0WhVGylrB-loU/edit?gid=1868453835#gid=1868453835</t>
+          <t>https://docs.google.com/spreadsheets/d/1o6ny97bUSd0JecsdBcnNSbmHQTZQETxla1QH6Ce87xk/edit?gid=16319423#gid=16319423</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Перевірено бюджет та внесено у докс по CF, https://docs.google.com/spreadsheets/d/1o6ny97bUSd0JecsdBcnNSbmHQTZQETxla1QH6Ce87xk/edit?gid=16319423#gid=16319423</t>
+          <t>Перевірено бюджет та внесено у докс по CF, https://docs.google.com/spreadsheets/d/1TIqsccnBXRHKmmJ9KpEN37lxyWHB1Vp8V5BVIrUERxg/edit?gid=1991782409#gid=1991782409</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Choice31</t>
+          <t>Black Ring</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1o6ny97bUSd0JecsdBcnNSbmHQTZQETxla1QH6Ce87xk/edit?gid=16319423#gid=16319423</t>
+          <t>https://docs.google.com/spreadsheets/d/1TIqsccnBXRHKmmJ9KpEN37lxyWHB1Vp8V5BVIrUERxg/edit?gid=1991782409#gid=1991782409</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Бюджетування: формування, коригування і консолідація плану</t>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Перевірено бюджет та внесено у докс по CF, https://docs.google.com/spreadsheets/d/13sILq-kZJl1dWXiFRhmYHtKg94nYH2Z70eBIJ7Lc2hc/edit?gid=1684866700#gid=1684866700</t>
+          <t>Не заповнено, https://docs.google.com/spreadsheets/d/1nr__kXUSm1gau-kxYRqKvRvsmn77jxxjQ22ATszKzfo/edit?gid=449082110#gid=449082110</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tonti Laguna Prime</t>
+          <t>Serpstat</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>03-02-2025</t>
+          <t>17-02-2025</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1692,11 +1692,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1705,23 +1705,23 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Бюджетування: формування, коригування і консолідація плану</t>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Категорія В:
-коригування до бюджету</t>
+формування вибірки даних+аналіз</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/13sILq-kZJl1dWXiFRhmYHtKg94nYH2Z70eBIJ7Lc2hc/edit?gid=1684866700#gid=1684866700</t>
+          <t>https://docs.google.com/spreadsheets/d/1nr__kXUSm1gau-kxYRqKvRvsmn77jxxjQ22ATszKzfo/edit?gid=449082110#gid=449082110</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1733,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Бюджетування: формування, коригування і консолідація плану</t>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Перевірено бюджет та внесено у докс по CF, https://docs.google.com/spreadsheets/d/1TIqsccnBXRHKmmJ9KpEN37lxyWHB1Vp8V5BVIrUERxg/edit?gid=1991782409#gid=1991782409</t>
+          <t>Сформовано план надходжень в розрізі ФОПів на поточний місяць, перевірено що ліміти не будуть перевищені, повідомлено про це Гаріку і Косу. Якщо ліміти по якомусь фопу підходять, то підібрана заміна, узгоджена з Косом і Гаріком. Якщо немає відкритого валютного рахунку, то був зроблений запит на Стоїка про відкриття рахунку в банку. Поставлені задачі на відкриття фоп, якщо немає вільних для отримання виплат., https://docs.google.com/spreadsheets/d/1BrJuQMiOSnd79VRIUUmsDqT9gADTZk0ayQ5GwrY6EcM/edit#gid=602441903</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Black Ring</t>
+          <t>Tonti Laguna Prime</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>03-02-2025</t>
+          <t>10-02-2025</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1778,11 +1778,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1791,23 +1791,23 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Бюджетування: формування, коригування і консолідація плану</t>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Категорія В:
-коригування до бюджету</t>
+          <t>Категорія А:
+формування вибірки даних</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1TIqsccnBXRHKmmJ9KpEN37lxyWHB1Vp8V5BVIrUERxg/edit?gid=1991782409#gid=1991782409</t>
+          <t>https://docs.google.com/spreadsheets/d/1BrJuQMiOSnd79VRIUUmsDqT9gADTZk0ayQ5GwrY6EcM/edit#gid=602441903</t>
         </is>
       </c>
     </row>
@@ -1819,1280 +1819,1282 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Не заповнено, https://docs.google.com/spreadsheets/d/17sa6XMSEQMEPMn1hiO5B9AANsgChfRNFgDJov46zKfY/edit#gid=1407639626</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Serpstat</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Сергей Vert Брагаренко</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>537</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>20.02</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/17sa6XMSEQMEPMn1hiO5B9AANsgChfRNFgDJov46zKfY/edit#gid=1407639626</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>проведена звірка за січень, https://docs.google.com/spreadsheets/d/1hl9JD14q-vmSxleNy_2PslppBk39lgggZd5zQjb8nPI/edit?gid=2052352866#gid=2052352866</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Розподільний (послуги оплачує декілька компаній | услуги оплачивают несколько компаний)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Розподіл
+UA - 60%, KZ - 20%, radASO -15%, OLX - 5% </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>552</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>120.12</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1hl9JD14q-vmSxleNy_2PslppBk39lgggZd5zQjb8nPI/edit?gid=2052352866#gid=2052352866</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>проведена звірка в лютому за січень, Рингостат ссылка
+Ринго БГ ссылка</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ringostat: General</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10-02-2025</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10-02-2025</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Анна Lunna Яковуник</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>536</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>180.18</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Рингостат ссылка
+Ринго БГ ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Не заповнено, https://docs.google.com/spreadsheets/d/1YFkp6hOebm8Dq0svnhBfsHFhkOPs2hCV_FZd6iJtKP8/edit#gid=1071304362</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tonti Laguna Prime</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>02-02-2025</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Сергей Vert Брагаренко</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>538</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>20.02</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1YFkp6hOebm8Dq0svnhBfsHFhkOPs2hCV_FZd6iJtKP8/edit#gid=1071304362</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1. Оновлення даних (деталізації) напрямку в доксі
+2. Підготовка повідомлення в чат про виконання
+3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1rpJ5Lhn7HkMan0wdpHlprDXb5Q1UhnRVZKk4y-aWN70/edit?gid=1772544306#gid=1772544306</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (USA): General</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>12-02-2025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12-02-2025</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>576</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1rpJ5Lhn7HkMan0wdpHlprDXb5Q1UhnRVZKk4y-aWN70/edit?gid=1772544306#gid=1772544306</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1cQz-MKRGdZ1RTIzKfzL3-uP2sZoMCDsfRLXPbrKrXik/edit?gid=858929576#gid=858929576</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): SMM</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L22" t="n">
         <v>561</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>23.66</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1cQz-MKRGdZ1RTIzKfzL3-uP2sZoMCDsfRLXPbrKrXik/edit?gid=858929576#gid=858929576</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Звірка з іншими внутрішніми системами/бізнесами</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>проведена звірка в лютому за січень, Рингостат ссылка
-Ринго БГ ссылка</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ringostat: General</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Оновлення інформація по фантомним поповненням станом на грудень 2024, https://docs.google.com/spreadsheets/d/160eSTGKdIHVdXxjxTYxtb9mmH57PuLtmm9vvYBefoI4/edit?pli=1&amp;gid=783769395#gid=783769395</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (BG)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>10-02-2025</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10-02-2025</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Анна Lunna Яковуник</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>536</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>03-02-2025</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>553</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Звірка з іншими внутрішніми системами/бізнесами</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>180.18</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Рингостат ссылка
-Ринго БГ ссылка</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>20.02</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/160eSTGKdIHVdXxjxTYxtb9mmH57PuLtmm9vvYBefoI4/edit?pli=1&amp;gid=783769395#gid=783769395</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Звірка з іншими внутрішніми системами/бізнесами</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>проведена звірка за січень, https://docs.google.com/spreadsheets/d/1hl9JD14q-vmSxleNy_2PslppBk39lgggZd5zQjb8nPI/edit?gid=2052352866#gid=2052352866</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Проведена звірка за січень з плановими надходженнями по проєктах, https://docs.google.com/spreadsheets/d/1-8TfmTlJhxa8g6oUHynKkhEjVdHM02OViUaCkehknVQ/edit#gid=513868133</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>42n</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>02-02-2025</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Сергей Vert Брагаренко</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>539</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1-8TfmTlJhxa8g6oUHynKkhEjVdHM02OViUaCkehknVQ/edit#gid=513868133</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Аналіз чи можна працевлаштовувати людей на Кіпр, кого саме, https://docs.google.com/spreadsheets/d/1d-nbwdHXV9_bXJNM8KsNwx0eJs1iJnZJQLHb9ywlv4s/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KMA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>19-02-2025</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>19-02-2025</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Юлия Insomnia Кандалинцева</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>591</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Категорія В:
+формування вибірки даних+аналіз</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1d-nbwdHXV9_bXJNM8KsNwx0eJs1iJnZJQLHb9ywlv4s/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Проведено ретроспективу по статтях: Надходження рекламних бюджетів: інші джерела платного трафіку та Рекламні бюджети клієнтів: інші джерела платного трафіку за січень-лютий 2025 (зміна в запитах, календарних планах), внесення за новими статтям (DiVision, OLX, Megogo, AdX (Google), AdX (інші системи)), https://docs.google.com/spreadsheets/d/1U_jdipjV_nBtYC2exVltSz19Hhfo_6xj-a5sorjPqWg/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): General</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Розподільний (послуги оплачує декілька компаній | услуги оплачивают несколько компаний)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Розподіл
-UA - 60%, KZ - 20%, radASO -15%, OLX - 5% </t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>03-02-2025</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>03-02-2025</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>552</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>24-02-2025</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27-02-2025</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Oksana Seraphina Hrytsakova</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>606</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>120.12</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1hl9JD14q-vmSxleNy_2PslppBk39lgggZd5zQjb8nPI/edit?gid=2052352866#gid=2052352866</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>50.64</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1U_jdipjV_nBtYC2exVltSz19Hhfo_6xj-a5sorjPqWg/edit?gid=0#gid=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>незаповнено,</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Inweb</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>04-02-2025</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>28-02-2025</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yana Degtaria Dehtiarova</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>522</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>253.20</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
-3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1rpJ5Lhn7HkMan0wdpHlprDXb5Q1UhnRVZKk4y-aWN70/edit?gid=1772544306#gid=1772544306</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (USA): General</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=875521091#gid=875521091</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>576</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="L28" t="n">
+        <v>579</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>23.66</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1rpJ5Lhn7HkMan0wdpHlprDXb5Q1UhnRVZKk4y-aWN70/edit?gid=1772544306#gid=1772544306</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Не заповнено, https://docs.google.com/spreadsheets/d/17sa6XMSEQMEPMn1hiO5B9AANsgChfRNFgDJov46zKfY/edit#gid=1407639626</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Serpstat</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=875521091#gid=875521091</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Додано дані в звіт за 01.2025., https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=1143865815#gid=1143865815</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>03-02-2025</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Сергей Vert Брагаренко</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>537</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/17sa6XMSEQMEPMn1hiO5B9AANsgChfRNFgDJov46zKfY/edit#gid=1407639626</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Не заповнено, https://docs.google.com/spreadsheets/d/1YFkp6hOebm8Dq0svnhBfsHFhkOPs2hCV_FZd6iJtKP8/edit#gid=1071304362</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Tonti Laguna Prime</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>02-02-2025</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Сергей Vert Брагаренко</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>538</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1YFkp6hOebm8Dq0svnhBfsHFhkOPs2hCV_FZd6iJtKP8/edit#gid=1071304362</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Оновлення інформація по фантомним поповненням станом на грудень 2024, https://docs.google.com/spreadsheets/d/160eSTGKdIHVdXxjxTYxtb9mmH57PuLtmm9vvYBefoI4/edit?pli=1&amp;gid=783769395#gid=783769395</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (BG)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>03-02-2025</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>03-02-2025</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>06-02-2025</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>06-02-2025</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>553</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/160eSTGKdIHVdXxjxTYxtb9mmH57PuLtmm9vvYBefoI4/edit?pli=1&amp;gid=783769395#gid=783769395</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Проведена звірка за січень з плановими надходженнями по проєктах, https://docs.google.com/spreadsheets/d/1-8TfmTlJhxa8g6oUHynKkhEjVdHM02OViUaCkehknVQ/edit#gid=513868133</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>42n</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>02-02-2025</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Сергей Vert Брагаренко</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>539</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Звірка з іншими внутрішніми системами/бізнесами</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1-8TfmTlJhxa8g6oUHynKkhEjVdHM02OViUaCkehknVQ/edit#gid=513868133</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>442</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Аналіз чи можна працевлаштовувати людей на Кіпр, кого саме, https://docs.google.com/spreadsheets/d/1d-nbwdHXV9_bXJNM8KsNwx0eJs1iJnZJQLHb9ywlv4s/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>KMA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>19-02-2025</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>19-02-2025</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Юлия Insomnia Кандалинцева</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>591</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Категорія В:
-формування вибірки даних+аналіз</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1d-nbwdHXV9_bXJNM8KsNwx0eJs1iJnZJQLHb9ywlv4s/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Проведено ретроспективу по статтях: Надходження рекламних бюджетів: інші джерела платного трафіку та Рекламні бюджети клієнтів: інші джерела платного трафіку за січень-лютий 2025 (зміна в запитах, календарних планах), внесення за новими статтям (DiVision, OLX, Megogo, AdX (Google), AdX (інші системи)), https://docs.google.com/spreadsheets/d/1U_jdipjV_nBtYC2exVltSz19Hhfo_6xj-a5sorjPqWg/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27-02-2025</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Oksana Seraphina Hrytsakova</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>606</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>50.64</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1U_jdipjV_nBtYC2exVltSz19Hhfo_6xj-a5sorjPqWg/edit?gid=0#gid=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>незаповнено,</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Inweb</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>04-02-2025</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>28-02-2025</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Yana Degtaria Dehtiarova</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>522</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>253.20</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Категорія А:
+формування вибірки даних</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>52.77</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=1143865815#gid=1143865815</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Роботи по проекту
 1. Корекція та актуалізація планів проєкту Лютий 25
 2. Спринт зустрічі з командою проєкту Лютий 25,</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Netpeak Group</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>28-02-2025</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>28-02-2025</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Юлия Insomnia Кандалинцева</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L30" t="n">
         <v>607</v>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Категорія А:
 з фін. аналітиком</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>126.64</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
-3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=875521091#gid=875521091</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1V6Axi0L-ui0IZjTA_snpa0iePJ1Xqcg_BQoGiCNt5Jg/edit?gid=820345884#gid=820345884</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): E-mail</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>579</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="L31" t="n">
+        <v>563</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>23.66</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=875521091#gid=875521091</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Додано дані в звіт за 01.2025., https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=1143865815#gid=1143865815</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>06-02-2025</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>06-02-2025</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>442</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Категорія А:
-формування вибірки даних</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>52.77</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1NtDrylUPSiJzKeS6FftzSRVA5yIte-eQin36NFHDZiM/edit?gid=1143865815#gid=1143865815</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Додано дані в звіт за 01.2025., https://docs.google.com/spreadsheets/d/1UmLyTLD62i4NE6bKP0P0G0ObBaDcLxnK-EjNU2Ziq_s/edit?gid=1939687946#gid=1939687946</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>06-02-2025</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>06-02-2025</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>555</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1UmLyTLD62i4NE6bKP0P0G0ObBaDcLxnK-EjNU2Ziq_s/edit?gid=1939687946#gid=1939687946</t>
+          <t>https://docs.google.com/spreadsheets/d/1V6Axi0L-ui0IZjTA_snpa0iePJ1Xqcg_BQoGiCNt5Jg/edit?gid=820345884#gid=820345884</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3289,12 @@
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
-3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1V6Axi0L-ui0IZjTA_snpa0iePJ1Xqcg_BQoGiCNt5Jg/edit?gid=820345884#gid=820345884</t>
+3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1q2RxK9s08HY5kgmyPYjtXk9LJAJXiogvqjQoyt-tefM/edit?gid=890357696#gid=890357696</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Netpeak Agency (UA): E-mail</t>
+          <t>Netpeak Agency (UA): Telegram</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3331,7 +3333,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3356,7 +3358,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1V6Axi0L-ui0IZjTA_snpa0iePJ1Xqcg_BQoGiCNt5Jg/edit?gid=820345884#gid=820345884</t>
+          <t>https://docs.google.com/spreadsheets/d/1q2RxK9s08HY5kgmyPYjtXk9LJAJXiogvqjQoyt-tefM/edit?gid=890357696#gid=890357696</t>
         </is>
       </c>
     </row>
@@ -3373,14 +3375,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1. Оновлення даних (деталізації) напрямку в доксі
-2. Підготовка повідомлення в чат про виконання
-3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1q2RxK9s08HY5kgmyPYjtXk9LJAJXiogvqjQoyt-tefM/edit?gid=890357696#gid=890357696</t>
+          <t>Додано дані в звіт за 01.2025., https://docs.google.com/spreadsheets/d/1UmLyTLD62i4NE6bKP0P0G0ObBaDcLxnK-EjNU2Ziq_s/edit?gid=1939687946#gid=1939687946</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Netpeak Agency (UA): Telegram</t>
+          <t>Netpeak Agency (UA): General</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12-02-2025</t>
+          <t>06-02-2025</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12-02-2025</t>
+          <t>06-02-2025</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1q2RxK9s08HY5kgmyPYjtXk9LJAJXiogvqjQoyt-tefM/edit?gid=890357696#gid=890357696</t>
+          <t>https://docs.google.com/spreadsheets/d/1UmLyTLD62i4NE6bKP0P0G0ObBaDcLxnK-EjNU2Ziq_s/edit?gid=1939687946#gid=1939687946</t>
         </is>
       </c>
     </row>
@@ -3628,91 +3628,10 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
+          <t>Фінансове консультування по режиму Дія Сіті: моделювання та управління Cash Flow</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
-        <is>
-          <t>За погодженням ice, всі витрати збираємо на Netpeak Group (не розподіляємо на бізнеси),</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Netpeak Group</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>04-02-2025</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>28-02-2025</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Юлия Insomnia Кандалинцева</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>54.43</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>516</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>1378.17</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Фінансове консультування по режиму Дія Сіті: моделювання та управління Cash Flow</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>1. Розрахункова модель (збір, аналіз)
 2. Аналіз штатки та аналіз середньої 1200 євро
@@ -3722,9 +3641,90 @@
 6. Розрахунок дати звільнень, для середньої,</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Розподільний (послуги оплачує декілька компаній | услуги оплачивают несколько компаний)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Лінк на розподіл 02.2025 https://docs.google.com/spreadsheets/d/1NaiJsPXh9P4bvPtXMWrFCfp_9ZAu3cnh4wmtSMudysM/edit?gid=805250146#gid=805250146&amp;range=A1:C1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>04-02-2025</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25-02-2025</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Юлия Insomnia Кандалинцева</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>521</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Фінансове консультування по режиму Дія Сіті: моделювання та управління Cash Flow</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1816.10</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>За погодженням ice, всі витрати збираємо на Netpeak Group (не розподіляємо на бізнеси),</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Netpeak Agency (UA): General</t>
+          <t>Netpeak Group</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Розподільний (послуги оплачує декілька компаній | услуги оплачивают несколько компаний)</t>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Лінк на розподіл 02.2025 https://docs.google.com/spreadsheets/d/1NaiJsPXh9P4bvPtXMWrFCfp_9ZAu3cnh4wmtSMudysM/edit?gid=805250146#gid=805250146&amp;range=A1:C1</t>
+          <t xml:space="preserve">100% </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25-02-2025</t>
+          <t>28-02-2025</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>65.00</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Фінансове консультування по режиму Дія Сіті: моделювання та управління Cash Flow</t>
+          <t>Аналіз, розрахунок, коригування нових/старих фінансових процесів/даних</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1816.10</t>
+          <t>1378.17</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -3966,257 +3966,257 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1. Оновлення даних (деталізації) напрямку в доксі
+2. Підготовка повідомлення в чат про виконання
+3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1DTeeHzPkESaoSZ8K_B3ZrJqmM9AwYnPut2VHyS2KSDk/edit?gid=1442922348#gid=1442922348</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): Marketplace promotion</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12-02-2025</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12-02-2025</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>564</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1DTeeHzPkESaoSZ8K_B3ZrJqmM9AwYnPut2VHyS2KSDk/edit?gid=1442922348#gid=1442922348</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Бюджетування: формування, коригування і консолідація плану</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Проведено коригування, відповідно до потреб бізнесу, дві зустрічі по апдейтах, інтеграція готових бюджетів в фін. звіти, https://docs.google.com/spreadsheets/d/1FP8AfdGwP1nZgKhu6KffX9QDtvYfMuxVwgwAwWw5R4M/edit?gid=1859478927#gid=1859478927</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): General</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>28-02-2025</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="L43" t="n">
         <v>582</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>Бюджетування: формування, коригування і консолідація плану</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Категорія А:
 створення з нуля</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>106.45</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1FP8AfdGwP1nZgKhu6KffX9QDtvYfMuxVwgwAwWw5R4M/edit?gid=1859478927#gid=1859478927</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1bEO4DbylR8xSfL9ZfRyCoAGeSCNfuWuRuuxB6rpmnwY/edit?gid=1236931578#gid=1236931578</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): Finance</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="L44" t="n">
         <v>568</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>23.66</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1bEO4DbylR8xSfL9ZfRyCoAGeSCNfuWuRuuxB6rpmnwY/edit?gid=1236931578#gid=1236931578</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1. Оновлення даних (деталізації) напрямку в доксі
-2. Підготовка повідомлення в чат про виконання
-3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1DTeeHzPkESaoSZ8K_B3ZrJqmM9AwYnPut2VHyS2KSDk/edit?gid=1442922348#gid=1442922348</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): Marketplace promotion</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>12-02-2025</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>12-02-2025</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>564</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1DTeeHzPkESaoSZ8K_B3ZrJqmM9AwYnPut2VHyS2KSDk/edit?gid=1442922348#gid=1442922348</t>
         </is>
       </c>
     </row>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Оперативне планування CF лютий 2025, Saldo Apps Budget / Fin Model</t>
+          <t>Деталізація зарплати у звіті CF за січень 2025 року, https://docs.google.com/spreadsheets/d/1UlWgB1TQHqH4lHiGOo34FNmEkO8BVD3LO1yl5HYFAPA/edit?usp=sharing</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Saldo Apps</t>
+          <t>Netpeak New</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01-02-2025</t>
+          <t>06-02-2025</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>28-02-2025</t>
+          <t>21-02-2025</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4619,11 +4619,11 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Saldo Apps Budget / Fin Model</t>
+          <t>https://docs.google.com/spreadsheets/d/1UlWgB1TQHqH4lHiGOo34FNmEkO8BVD3LO1yl5HYFAPA/edit?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Деталізація зарплати у звіті CF за січень 2025 року, https://docs.google.com/spreadsheets/d/1UlWgB1TQHqH4lHiGOo34FNmEkO8BVD3LO1yl5HYFAPA/edit?usp=sharing</t>
+          <t>Оперативне планування CF лютий 2025, Saldo Apps Budget / Fin Model</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Netpeak New</t>
+          <t>Saldo Apps</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>06-02-2025</t>
+          <t>01-02-2025</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>21-02-2025</t>
+          <t>28-02-2025</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4705,11 +4705,11 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>35.18</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1UlWgB1TQHqH4lHiGOo34FNmEkO8BVD3LO1yl5HYFAPA/edit?usp=sharing</t>
+          <t>Saldo Apps Budget / Fin Model</t>
         </is>
       </c>
     </row>
@@ -5088,167 +5088,167 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Обговорили обороти юр. осіб Болгарії та Казахстану для ІАВ , http://img.netpeak.ua/sense/1136XYZ.jpg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>24-02-2025</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>24-02-2025</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>597</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Категорія А:
+з фін. аналітиком</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>7.92</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>http://img.netpeak.ua/sense/1136XYZ.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Деталізація зарплати у звіті CF за січень 2025 року, https://docs.google.com/spreadsheets/d/1XSQvIysrRPzZnm1QZtZ4kzChEYFLvyTfyaaCFsKRKT4/edit?gid=613198232#gid=613198232</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>KMA</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>11-02-2025</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>13-02-2025</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Vadym Stamford Didenko</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="L56" t="n">
         <v>593</v>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Категорія А:
 формування вибірки даних</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>43.98</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1XSQvIysrRPzZnm1QZtZ4kzChEYFLvyTfyaaCFsKRKT4/edit?gid=613198232#gid=613198232</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Обговорили обороти юр. осіб Болгарії та Казахстану для ІАВ , http://img.netpeak.ua/sense/1136XYZ.jpg</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>597</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Категорія А:
-з фін. аналітиком</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>7.92</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>http://img.netpeak.ua/sense/1136XYZ.jpg</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Розраховано додатковий відсоток комісії та необхідну суму вільних коштів для можливості кредитувати клієнта, https://docs.google.com/spreadsheets/d/1OhaV53yXIDfRcBonhz8pw9grfcG-RofCsxq0FnUrHLc/edit?gid=1310542865#gid=1310542865</t>
+          <t>Опрацьовано фоллоу ап по результатам зустрічей по аналізу кеш-флоу за січень 2025, https://docs.google.com/spreadsheets/d/1QPAnArv6KBoIF7YRNzv-Ota5JHURlzLVTa-f5sIfMiw/edit?gid=823291504#gid=823291504</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Netpeak Agency (KZ): SMM</t>
+          <t>Netpeak Agency (UA): General</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>06-02-2025</t>
+          <t>10-02-2025</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>06-02-2025</t>
+          <t>24-02-2025</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>526</v>
+        <v>599</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5411,18 +5411,18 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Категорія А:
-формування вибірки даних</t>
+          <t>Категорія В:
+формування вибірки даних+аналіз</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1OhaV53yXIDfRcBonhz8pw9grfcG-RofCsxq0FnUrHLc/edit?gid=1310542865#gid=1310542865</t>
+          <t>https://docs.google.com/spreadsheets/d/1QPAnArv6KBoIF7YRNzv-Ota5JHURlzLVTa-f5sIfMiw/edit?gid=823291504#gid=823291504</t>
         </is>
       </c>
     </row>
@@ -5434,333 +5434,333 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
-        <is>
-          <t>Опрацьовано фоллоу ап по результатам зустрічей по аналізу кеш-флоу за січень 2025, https://docs.google.com/spreadsheets/d/1QPAnArv6KBoIF7YRNzv-Ota5JHURlzLVTa-f5sIfMiw/edit?gid=823291504#gid=823291504</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>10-02-2025</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>599</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Категорія В:
-формування вибірки даних+аналіз</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>47.32</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1QPAnArv6KBoIF7YRNzv-Ota5JHURlzLVTa-f5sIfMiw/edit?gid=823291504#gid=823291504</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Огляд звіту за січень по аналітикам (статтям/проєктам), http://img.netpeak.ua/sense/1136HH1.jpg</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>596</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Категорія А:
-з фін. аналітиком</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>http://img.netpeak.ua/sense/1136HH1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Аналітика за 2024 витрат по зарплаті в розрізі команд, співвідношення з NR по проєктам, https://docs.google.com/spreadsheets/d/1Nzm3WuKaqkWV8JaRgFX4ey_9CYtEaYiQpxetbGTyOdQ/edit?gid=1361440420#gid=1361440420</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>RadASO: General</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>20-02-2025</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20-02-2025</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>592</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1Nzm3WuKaqkWV8JaRgFX4ey_9CYtEaYiQpxetbGTyOdQ/edit?gid=1361440420#gid=1361440420</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
         <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1-3IECeszDv0F-nr1h7gtLVkUCK_DjdD8CaFz95jkV4c/edit?gid=534335259#gid=534335259</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): Linkbuilding</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="L59" t="n">
         <v>559</v>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1-3IECeszDv0F-nr1h7gtLVkUCK_DjdD8CaFz95jkV4c/edit?gid=534335259#gid=534335259</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Розраховано додатковий відсоток комісії та необхідну суму вільних коштів для можливості кредитувати клієнта, https://docs.google.com/spreadsheets/d/1OhaV53yXIDfRcBonhz8pw9grfcG-RofCsxq0FnUrHLc/edit?gid=1310542865#gid=1310542865</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (KZ): SMM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>06-02-2025</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>06-02-2025</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>526</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Підготовка додаткової аналітики/вибірки для бізнесу</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Категорія А:
+формування вибірки даних</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>17.59</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1OhaV53yXIDfRcBonhz8pw9grfcG-RofCsxq0FnUrHLc/edit?gid=1310542865#gid=1310542865</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Огляд звіту за січень по аналітикам (статтям/проєктам), http://img.netpeak.ua/sense/1136HH1.jpg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>24-02-2025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>24-02-2025</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>596</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Проведення зустрічі/надання консультації з фінансових питань/звітів/аналітики</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Категорія А:
+з фін. аналітиком</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>31.66</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>http://img.netpeak.ua/sense/1136HH1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Аналітика за 2024 витрат по зарплаті в розрізі команд, співвідношення з NR по проєктам, https://docs.google.com/spreadsheets/d/1Nzm3WuKaqkWV8JaRgFX4ey_9CYtEaYiQpxetbGTyOdQ/edit?gid=1361440420#gid=1361440420</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RadASO: General</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>20-02-2025</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20-02-2025</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>592</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>23.66</t>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1-3IECeszDv0F-nr1h7gtLVkUCK_DjdD8CaFz95jkV4c/edit?gid=534335259#gid=534335259</t>
+          <t>https://docs.google.com/spreadsheets/d/1Nzm3WuKaqkWV8JaRgFX4ey_9CYtEaYiQpxetbGTyOdQ/edit?gid=1361440420#gid=1361440420</t>
         </is>
       </c>
     </row>
@@ -6134,156 +6134,156 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Пораховано вплив переходу працівників в ДіяСіті на CF по бізнес-ютітам NAG за грудень 2024, https://docs.google.com/spreadsheets/d/1g-zGB-yfub26VmNdMLkxmNweRE32tJZjQfgoPnoMcEg/edit?gid=1785354910#gid=1785354910</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>07-02-2025</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>07-02-2025</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>529</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1g-zGB-yfub26VmNdMLkxmNweRE32tJZjQfgoPnoMcEg/edit?gid=1785354910#gid=1785354910</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/1Oxz7JjMDmswTZvfuu1HGkZofL7yeU9LTI8oaDHAJ9BM/edit?gid=385350546#gid=385350546</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Netpeak Agency (UA): Usability</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L68" t="n">
+      <c r="L67" t="n">
         <v>571</v>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1Oxz7JjMDmswTZvfuu1HGkZofL7yeU9LTI8oaDHAJ9BM/edit?gid=385350546#gid=385350546</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Пораховано вплив переходу працівників в ДіяСіті на CF по бізнес-ютітам NAG за грудень 2024, https://docs.google.com/spreadsheets/d/1g-zGB-yfub26VmNdMLkxmNweRE32tJZjQfgoPnoMcEg/edit?gid=1785354910#gid=1785354910</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>07-02-2025</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>07-02-2025</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>529</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>23.66</t>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1Oxz7JjMDmswTZvfuu1HGkZofL7yeU9LTI8oaDHAJ9BM/edit?gid=385350546#gid=385350546</t>
+          <t>https://docs.google.com/spreadsheets/d/1g-zGB-yfub26VmNdMLkxmNweRE32tJZjQfgoPnoMcEg/edit?gid=1785354910#gid=1785354910</t>
         </is>
       </c>
     </row>
@@ -6654,156 +6654,156 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Вивантажено витрати по постачальникам, статті витрат, сумі (від більшого до меншого) ТОВ “Нетпік” за грудень 2024-січень 2025, https://docs.google.com/spreadsheets/d/1uuRiPanLTDSp1aExvZyiItV7Phf8yTskU7KuU9Wch84/edit?gid=1111770543#gid=1111770543</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NC UA-accounting team</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>11-02-2025</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>13-02-2025</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>583</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1uuRiPanLTDSp1aExvZyiItV7Phf8yTskU7KuU9Wch84/edit?gid=1111770543#gid=1111770543</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
           <t>1. Оновлення даних (деталізації) напрямку в доксі
 2. Підготовка повідомлення в чат про виконання
 3. Аналітика витрат, доходів, https://docs.google.com/spreadsheets/d/19ZET9deMpFZeOlD54Q-PbLcP7MGYcfKZCfSJWFvsnxA/edit?gid=85017413#gid=85017413</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>RadASO: General</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">100% </t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>12-02-2025</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Олександр Sense Штефан</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L74" t="n">
+      <c r="L73" t="n">
         <v>573</v>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>Категорія В:
 внесення коригувань</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/19ZET9deMpFZeOlD54Q-PbLcP7MGYcfKZCfSJWFvsnxA/edit?gid=85017413#gid=85017413</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Вивантажено витрати по постачальникам, статті витрат, сумі (від більшого до меншого) ТОВ “Нетпік” за грудень 2024-січень 2025, https://docs.google.com/spreadsheets/d/1uuRiPanLTDSp1aExvZyiItV7Phf8yTskU7KuU9Wch84/edit?gid=1111770543#gid=1111770543</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NC UA-accounting team</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>13-02-2025</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>583</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>23.66</t>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/19ZET9deMpFZeOlD54Q-PbLcP7MGYcfKZCfSJWFvsnxA/edit?gid=85017413#gid=85017413</t>
+          <t>https://docs.google.com/spreadsheets/d/1uuRiPanLTDSp1aExvZyiItV7Phf8yTskU7KuU9Wch84/edit?gid=1111770543#gid=1111770543</t>
         </is>
       </c>
     </row>
@@ -6997,10 +6997,96 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Сформовано звіт надходжень за 2024 на юридичні особи Болгарії та Казахстану без внутрішньогрупових оборотів для ІАВ в розрізі валют та платіжних систем, виділено частку NA України, https://docs.google.com/spreadsheets/d/1oMGjpbg73at4zKY6vuVICPTDxD7eOi1lAYAGon_Wms8/edit?gid=1856181411#gid=1856181411</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Netpeak Agency (UA): General</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% </t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>21-02-2025</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>24-02-2025</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Олександр Sense Штефан</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>598</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Категорія В:
+внесення коригувань</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1oMGjpbg73at4zKY6vuVICPTDxD7eOi1lAYAGon_Wms8/edit?gid=1856181411#gid=1856181411</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Назва</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Фінансове консультування по режиму Дія Сіті: моделювання та управління Cash Flow</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>1. Розрахункова модель (збір ЗП, аналіз)
 2. Аналіз штатки та аналіз середньої 1200 євро
@@ -7010,156 +7096,70 @@
 6. Розрахунок дати звільнень, для середньої,</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Ringostat: General</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Finance P&amp;A</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Розподільний (послуги оплачує декілька компаній | услуги оплачивают несколько компаний)</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Лінк на розподіл 02.2025 https://docs.google.com/spreadsheets/d/1TYrYCNgLgdEjhCX9-zM-HPC9h-JyCMwnA54AGOSwFRg/edit?gid=1410878660#gid=1410878660&amp;range=A1:C1</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>04-02-2025</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>25-02-2025</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Юлия Insomnia Кандалинцева</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="L77" t="n">
+      <c r="L78" t="n">
         <v>518</v>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Завершене</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>Фінансове консультування по режиму Дія Сіті: моделювання та управління Cash Flow</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>1341.12</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Назва</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Сформовано звіт надходжень за 2024 на юридичні особи Болгарії та Казахстану без внутрішньогрупових оборотів для ІАВ в розрізі валют та платіжних систем, виділено частку NA України, https://docs.google.com/spreadsheets/d/1oMGjpbg73at4zKY6vuVICPTDxD7eOi1lAYAGon_Wms8/edit?gid=1856181411#gid=1856181411</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Netpeak Agency (UA): General</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Finance P&amp;A</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Прямий (послуги оплачує компанія-замовник | услуги оплачивает компания-заказчик)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100% </t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>21-02-2025</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>24-02-2025</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Олександр Sense Штефан</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>598</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Завершене</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Налаштування оперативних фінансових репортів, дашбордів та інфографіки</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Категорія В:
-внесення коригувань</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1oMGjpbg73at4zKY6vuVICPTDxD7eOi1lAYAGon_Wms8/edit?gid=1856181411#gid=1856181411</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
